--- a/recetasColombianas.xlsx
+++ b/recetasColombianas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Andrees\Descargas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Andrees\Escritorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FCC4CA7-089E-4A14-8A18-A4249F273EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1768A88F-3CC5-4D3D-B032-ACAA117A78E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="359">
   <si>
     <t>titulo</t>
   </si>
@@ -207,6 +207,9 @@
     <t>Huevos Pericos</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Huevos_Pericos_gbzaan</t>
+  </si>
+  <si>
     <t>Huevos 3 unidad; Tomate 1 unidad; Cebolla larga 2 unidad; Aceite 1 cucharada; Sal al gusto; Cilantro al gusto</t>
   </si>
   <si>
@@ -216,6 +219,9 @@
     <t>Chocolate Santafeno con Almojabana</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Chocolate_Santafeno_con_Almojabana_amahs7</t>
+  </si>
+  <si>
     <t>Chocolate en tableta 2 unidad; Leche 500ml; Almojabanas 4 unidad; Queso campesino 100g; Agua 250ml</t>
   </si>
   <si>
@@ -225,6 +231,9 @@
     <t>Tamal Tolimense</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Tamal_ldb6vn</t>
+  </si>
+  <si>
     <t>Masa de maiz 500g; Cerdo 300g; Pollo 200g; Papa 200g; Zanahoria 1 unidad; Arveja 100g; Hogao 4 cucharadas; Hojas de platano al gusto; Sal y comino al gusto</t>
   </si>
   <si>
@@ -234,6 +243,9 @@
     <t>Envueltos de Choclo</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Envueltos_de_krbk0k</t>
+  </si>
+  <si>
     <t>Maiz tierno 6 mazorcas; Azucar 3 cucharadas; Sal 1 cucharadita; Mantequilla 50g; Hojas de choclo al gusto</t>
   </si>
   <si>
@@ -243,6 +255,9 @@
     <t>Frijoles Antioquenos</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Frijoles_Antioquen_jbpugy</t>
+  </si>
+  <si>
     <t>Frijoles cargamanto 500g; Hogao 4 cucharadas; Chicharron 150g; Platano verde 1 unidad; Papa 2 unidad; Comino 1 cucharadita; Sal al gusto; Cilantro al gusto</t>
   </si>
   <si>
@@ -252,6 +267,9 @@
     <t>Sopa de Mondongo</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Sopa_de_Mondong_wwhpas</t>
+  </si>
+  <si>
     <t>Mondongo 800g; Papa 3 unidad; Yuca 200g; Zanahoria 1 unidad; Cebolla 1 unidad; Ajo 4 dientes; Comino 1 cucharadita; Cilantro al gusto; Sal al gusto</t>
   </si>
   <si>
@@ -261,6 +279,9 @@
     <t>Sobrebarriga en Salsa</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Sobrebarriga_en_xhmam0</t>
+  </si>
+  <si>
     <t>Sobrebarriga 800g; Tomate 3 unidad; Cebolla 1 unidad; Ajo 4 dientes; Pimenton 1 unidad; Comino 1 cucharadita; Color 1 cucharadita; Sal al gusto</t>
   </si>
   <si>
@@ -270,6 +291,9 @@
     <t>Cazuela de Mariscos</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/mariscos_bhlfnw</t>
+  </si>
+  <si>
     <t>Camarones 300g; Calamares 200g; Almejas 200g; Leche de coco 200ml; Tomate 2 unidad; Cebolla 1 unidad; Ajo 3 dientes; Cilantro al gusto; Sal al gusto</t>
   </si>
   <si>
@@ -279,6 +303,9 @@
     <t>Caldo de Costilla</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/caldo_de_costilla_yevery</t>
+  </si>
+  <si>
     <t>Costilla de res 600g; Papa 3 unidad; Cebolla larga 2 unidad; Ajo 3 dientes; Cilantro al gusto; Comino 1 cucharadita; Sal al gusto</t>
   </si>
   <si>
@@ -288,6 +315,9 @@
     <t>Crema de Ahuyama</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/crema_ahuyana_t2frmg</t>
+  </si>
+  <si>
     <t>Ahuyama 600g; Cebolla 1 unidad; Ajo 2 dientes; Crema de leche 100ml; Caldo de pollo 500ml; Mantequilla 20g; Sal y pimienta al gusto</t>
   </si>
   <si>
@@ -297,6 +327,9 @@
     <t>Posta Negra Cartagenera</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/posta_negra_cartagenera_i5l8os</t>
+  </si>
+  <si>
     <t>Morro de res 1kg; Panela 100g; Cola cola 350ml; Cebolla 1 unidad; Ajo 4 dientes; Tomillo al gusto; Laurel 2 hojas; Sal y pimienta al gusto</t>
   </si>
   <si>
@@ -306,6 +339,9 @@
     <t>Sudado de Pollo</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/sudado_de_pollo_cltpyi</t>
+  </si>
+  <si>
     <t>Pollo 800g; Tomate 3 unidad; Cebolla 1 unidad; Ajo 3 dientes; Papa 3 unidad; Color 1 cucharadita; Comino 1 cucharadita; Cilantro al gusto; Sal al gusto</t>
   </si>
   <si>
@@ -315,6 +351,9 @@
     <t>Aborrajados</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/aborrajados_rg9glg</t>
+  </si>
+  <si>
     <t>Platano maduro 2 unidad; Queso campesino 100g; Huevo 2 unidad; Harina 4 cucharadas; Aceite para freir; Sal al gusto</t>
   </si>
   <si>
@@ -324,64 +363,745 @@
     <t>Arepa de Huevo</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/arepa_de_heuvo_vgkkvt</t>
+  </si>
+  <si>
     <t>Harina de maiz 300g; Huevos 4 unidad; Aceite para freir; Sal al gusto; Agua tibia al gusto</t>
   </si>
   <si>
     <t>Preparar la masa con harina agua tibia y sal; Formar discos y freir en aceite caliente hasta inflar; Abrir un pequeno orificio e introducir un huevo; Cerrar el orificio y freir 2 minutos mas; Escurrir y servir caliente</t>
   </si>
   <si>
+    <t>Buñuelos</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/buñuelo_ikcr4p</t>
+  </si>
+  <si>
     <t>Almidon de yuca 200g; Queso blanco rallado 150g; Huevo 1 unidad; Sal 1 cucharadita; Azucar 1 cucharadita; Aceite para freir</t>
   </si>
   <si>
     <t>Mezclar el almidon con el queso rallado; Agregar el huevo sal y azucar; Amasar hasta obtener masa suave; Formar bolitas medianas; Freir en aceite caliente hasta dorar y flotar; Escurrir y servir calientes</t>
   </si>
   <si>
-    <t>Buñuelos</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Huevos_Pericos_gbzaan</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Chocolate_Santafeno_con_Almojabana_amahs7</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Tamal_ldb6vn</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Envueltos_de_krbk0k</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Frijoles_Antioquen_jbpugy</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Sopa_de_Mondong_wwhpas</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Sobrebarriga_en_xhmam0</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/mariscos_bhlfnw</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/caldo_de_costilla_yevery</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/crema_ahuyana_t2frmg</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/posta_negra_cartagenera_i5l8os</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/sudado_de_pollo_cltpyi</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/aborrajados_rg9glg</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/arepa_de_heuvo_vgkkvt</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/buñuelo_ikcr4p</t>
+    <t>Arepa con Hogao</t>
+  </si>
+  <si>
+    <t>Arepa de maiz 4 unidad; Tomate 3 unidad; Cebolla larga 3 unidad; Aceite 2 cucharadas; Sal al gusto; Cilantro al gusto</t>
+  </si>
+  <si>
+    <t>Picar tomate y cebolla finamente; Sofreir en aceite hasta formar salsa espesa; Sazonar con sal y cilantro; Calentar las arepas en budare; Servir con hogao encima</t>
+  </si>
+  <si>
+    <t>Arepas de Choclo Rellenas</t>
+  </si>
+  <si>
+    <t>Maiz tierno molido 400g; Queso doble crema 200g; Jamon 150g; Mantequilla 30g; Sal al gusto</t>
+  </si>
+  <si>
+    <t>Mezclar maiz molido con sal y mantequilla; Formar discos de masa; Rellenar con queso y jamon; Sellar los bordes; Cocinar en sarten 5 minutos por lado</t>
+  </si>
+  <si>
+    <t>Caldo de Huevo</t>
+  </si>
+  <si>
+    <t>Huevos 2 unidad; Cebolla larga 2 unidad; Cilantro al gusto; Sal al gusto; Agua 500ml</t>
+  </si>
+  <si>
+    <t>Hervir el agua con cebolla y sal; Romper los huevos en el caldo hirviendo; Cocinar 3 minutos; Agregar cilantro; Servir caliente con arepa</t>
+  </si>
+  <si>
+    <t>Mogolla con Queso</t>
+  </si>
+  <si>
+    <t>Mogolla 2 unidad; Queso campesino 100g; Mantequilla 20g; Chocolate 2 tazas</t>
+  </si>
+  <si>
+    <t>Partir las mogollas por la mitad; Untar mantequilla; Agregar queso campesino; Preparar el chocolate caliente; Servir juntos</t>
+  </si>
+  <si>
+    <t>Natilla con Buneulos</t>
+  </si>
+  <si>
+    <t>Leche 1 litro; Maizena 100g; Panela 200g; Clavos 3 unidad; Canela 1 astilla; Almidon de yuca 200g; Queso blanco 150g; Huevo 1 unidad</t>
+  </si>
+  <si>
+    <t>Disolver maizena en leche fria; Agregar panela clavos y canela; Cocinar revolviendo hasta espesar; Verter en molde y dejar enfriar; Preparar buneulos mezclando almidon queso y huevo; Freir hasta dorar</t>
+  </si>
+  <si>
+    <t>Hervido de Frutas</t>
+  </si>
+  <si>
+    <t>Mora 200g; Guanabana 200g; Lulo 3 unidad; Maracuya 2 unidad; Azucar al gusto; Agua 1 litro</t>
+  </si>
+  <si>
+    <t>Hervir el agua con azucar; Agregar todas las frutas; Cocinar 10 minutos a fuego medio; Colar y servir caliente; Acompanar con pan o arepa</t>
+  </si>
+  <si>
+    <t>Arepa de Maiz Pelao</t>
+  </si>
+  <si>
+    <t>Maiz pelao 500g; Sal al gusto; Agua al gusto</t>
+  </si>
+  <si>
+    <t>Moler el maiz pelao cocido; Amasar con sal y agua tibia; Formar arepas medianas; Cocinar en budare a fuego medio; Voltear hasta dorar por ambos lados; Servir caliente</t>
+  </si>
+  <si>
+    <t>Masato de Arroz</t>
+  </si>
+  <si>
+    <t>Arroz 300g; Agua 2 litros; Azucar 150g; Canela 2 astillas; Clavos 4 unidad</t>
+  </si>
+  <si>
+    <t>Cocinar el arroz con canela y clavos; Licuar hasta obtener bebida homogenea; Colar y agregar azucar; Hervir nuevamente 10 minutos; Servir frio o caliente</t>
+  </si>
+  <si>
+    <t>Obleas con Arequipe</t>
+  </si>
+  <si>
+    <t>Obleas 8 unidad; Arequipe 200g; Queso rallado 100g; Mermelada de mora 4 cucharadas</t>
+  </si>
+  <si>
+    <t>Extender arequipe sobre una oblea; Agregar queso rallado; Colocar mermelada al gusto; Cubrir con otra oblea; Servir de inmediato</t>
+  </si>
+  <si>
+    <t>Sancocho de Pescado</t>
+  </si>
+  <si>
+    <t>Pescado bagre 600g; Yuca 300g; Platano verde 1 unidad; Cebolla 1 unidad; Ajo 3 dientes; Cilantro al gusto; Sal y comino al gusto</t>
+  </si>
+  <si>
+    <t>Sazonar el pescado con sal ajo y comino; Hervir agua con cebolla; Agregar yuca y platano; Cocinar 15 minutos; Agregar el pescado; Cocinar 15 minutos mas; Servir con cilantro</t>
+  </si>
+  <si>
+    <t>Aguapanela con Queso</t>
+  </si>
+  <si>
+    <t>Panela 150g; Agua 1 litro; Queso campesino 150g; Limon 1 unidad</t>
+  </si>
+  <si>
+    <t>Disolver la panela en agua caliente; Agregar unas gotas de limon; Cortar el queso en cubos; Sumergir el queso en la aguapanela caliente; Servir en taza</t>
+  </si>
+  <si>
+    <t>Tamales de Pipian</t>
+  </si>
+  <si>
+    <t>Masa de maiz 500g; Pipian 200g; Papa 300g; Hogao 4 cucharadas; Hojas de platano al gusto; Sal al gusto</t>
+  </si>
+  <si>
+    <t>Preparar la masa con sal y hogao; Cocinar el pipian con hogao; Extender masa en hojas; Rellenar con pipian y papa; Envolver y amarrar; Cocinar 1 hora en agua</t>
+  </si>
+  <si>
+    <t>Crispetas de Maiz</t>
+  </si>
+  <si>
+    <t>Maiz pira 150g; Aceite 2 cucharadas; Sal al gusto; Mantequilla 20g</t>
+  </si>
+  <si>
+    <t>Calentar aceite en olla con tapa; Agregar el maiz pira; Tapar y agitar constantemente; Cocinar hasta que deje de reventar; Agregar mantequilla y sal; Servir caliente</t>
+  </si>
+  <si>
+    <t>Colada de Avena</t>
+  </si>
+  <si>
+    <t>Avena en hojuelas 200g; Leche 1 litro; Canela 1 astilla; Azucar al gusto; Clavos 2 unidad</t>
+  </si>
+  <si>
+    <t>Licuar la avena con leche; Colar la mezcla; Cocinar a fuego medio con canela y clavos; Revolver constantemente; Agregar azucar al gusto; Servir caliente</t>
+  </si>
+  <si>
+    <t>Arepas de Pipian</t>
+  </si>
+  <si>
+    <t>Maiz trillado 400g; Pipian 200g; Hogao 3 cucharadas; Sal al gusto</t>
+  </si>
+  <si>
+    <t>Cocinar el maiz trillado hasta suavizar; Moler y amasar con sal; Cocinar el pipian con hogao; Rellenar las arepas con pipian; Cocinar en budare 5 minutos por lado</t>
+  </si>
+  <si>
+    <t>Viudo de Pescado</t>
+  </si>
+  <si>
+    <t>Pescado bocachico 800g; Yuca 400g; Platano verde 2 unidad; Papa 3 unidad; Cebolla 1 unidad; Tomate 2 unidad; Cilantro al gusto; Sal al gusto</t>
+  </si>
+  <si>
+    <t>Limpiar el pescado y sazonar; Armar capas en olla con yuca platano y papa; Colocar el pescado encima; Agregar hogao y agua; Tapar y cocinar a fuego bajo 40 minutos; Servir con cilantro</t>
+  </si>
+  <si>
+    <t>Pepitoria de Cabro</t>
+  </si>
+  <si>
+    <t>Cabro 800g; Higado 200g; Papas 300g; Cebolla 1 unidad; Ajo 4 dientes; Cilantro al gusto; Comino al gusto; Sal al gusto</t>
+  </si>
+  <si>
+    <t>Cocinar el cabro con sal comino y ajo; Sofreir higado con cebolla; Mezclar carnes con papa cocida; Sazonar con cilantro; Cocinar 20 minutos mas; Servir con arepa</t>
+  </si>
+  <si>
+    <t>Cocido Boyacense</t>
+  </si>
+  <si>
+    <t>Papa criolla 300g; Arveja 200g; Haba 200g; Maiz 200g; Carne de cerdo 400g; Longaniza 2 unidad; Mazorca 2 unidad; Sal y comino al gusto</t>
+  </si>
+  <si>
+    <t>Cocinar la carne y longaniza con sal; Agregar arveja haba y maiz; Cocinar 20 minutos; Agregar papa criolla y mazorca; Cocinar 20 minutos mas; Servir todo junto</t>
+  </si>
+  <si>
+    <t>Lengua en Salsa</t>
+  </si>
+  <si>
+    <t>Lengua de res 1kg; Tomate 4 unidad; Cebolla 2 unidad; Ajo 6 dientes; Pimenton 1 unidad; Comino al gusto; Sal al gusto</t>
+  </si>
+  <si>
+    <t>Cocinar la lengua en olla a presion 45 minutos; Pelar y cortar en rodajas; Licuar tomate cebolla ajo y pimenton; Sofreir la salsa; Agregar la lengua en rodajas; Cocinar 20 minutos en salsa</t>
+  </si>
+  <si>
+    <t>Arroz de Coco con Mariscos</t>
+  </si>
+  <si>
+    <t>Arroz 300g; Leche de coco 400ml; Camarones 300g; Calamares 200g; Cebolla 1 unidad; Ajo 3 dientes; Sal al gusto</t>
+  </si>
+  <si>
+    <t>Cocinar el arroz con leche de coco y sal; Sofreir cebolla y ajo; Agregar mariscos y saltear; Mezclar con el arroz de coco; Cocinar 5 minutos mas; Servir caliente</t>
+  </si>
+  <si>
+    <t>Cuchuco de Trigo</t>
+  </si>
+  <si>
+    <t>Trigo partido 300g; Costilla de cerdo 400g; Papa criolla 200g; Arveja 150g; Habas 150g; Cebolla 1 unidad; Ajo 3 dientes; Sal al gusto</t>
+  </si>
+  <si>
+    <t>Cocinar el trigo con agua sal y cebolla; Agregar la costilla de cerdo; Cocinar 30 minutos; Agregar papa arveja y habas; Cocinar 20 minutos mas; Servir caliente</t>
+  </si>
+  <si>
+    <t>Sopa de Tortilla</t>
+  </si>
+  <si>
+    <t>Tortillas de maiz 6 unidad; Pollo 400g; Tomate 2 unidad; Cebolla 1 unidad; Ajo 2 dientes; Cilantro al gusto; Sal al gusto</t>
+  </si>
+  <si>
+    <t>Cocinar el pollo y desmechar; Sofreir tomate cebolla y ajo; Agregar caldo de pollo; Cortar tortillas en tiras y freir; Agregar al caldo con el pollo; Servir con cilantro</t>
+  </si>
+  <si>
+    <t>Estofado de Res</t>
+  </si>
+  <si>
+    <t>Carne de res 600g; Papa 3 unidad; Zanahoria 2 unidad; Arveja 100g; Tomate 2 unidad; Cebolla 1 unidad; Sal y comino al gusto</t>
+  </si>
+  <si>
+    <t>Cortar la carne en cubos y sellar; Agregar tomate cebolla y especias; Cubrir con agua y cocinar 40 minutos; Agregar papa zanahoria y arveja; Cocinar 20 minutos mas; Servir con arroz</t>
+  </si>
+  <si>
+    <t>Chuleta Valle</t>
+  </si>
+  <si>
+    <t>Chuleta de cerdo 2 unidad; Limon 2 unidad; Ajo 4 dientes; Sal y pimienta al gusto; Aceite 2 cucharadas</t>
+  </si>
+  <si>
+    <t>Marinar las chuletas con limon ajo sal y pimienta; Dejar 30 minutos en nevera; Calentar aceite en sarten; Freir las chuletas 8 minutos por lado; Servir con papas y ensalada</t>
+  </si>
+  <si>
+    <t>Sopa de Ahuyama</t>
+  </si>
+  <si>
+    <t>Ahuyama 500g; Papa 2 unidad; Cebolla 1 unidad; Ajo 2 dientes; Cilantro al gusto; Sal al gusto; Crema de leche 100ml</t>
+  </si>
+  <si>
+    <t>Sofreir cebolla y ajo; Agregar ahuyama y papa en cubos; Cubrir con agua y cocinar 25 minutos; Licuar parcialmente; Agregar crema y sazonar; Servir con cilantro</t>
+  </si>
+  <si>
+    <t>Mojarra Frita</t>
+  </si>
+  <si>
+    <t>Mojarra 2 unidad; Limon 2 unidad; Ajo 3 dientes; Sal al gusto; Comino al gusto; Aceite para freir</t>
+  </si>
+  <si>
+    <t>Limpiar las mojarras y hacer cortes; Marinar con limon ajo sal y comino; Calentar abundante aceite; Freir las mojarras 6 minutos por lado; Escurrir y servir con patacones y ensalada</t>
+  </si>
+  <si>
+    <t>Puchero Bogotano</t>
+  </si>
+  <si>
+    <t>Carne de res 300g; Pollo 300g; Papa 3 unidad; Yuca 200g; Mazorca 2 unidad; Zanahoria 2 unidad; Cebolla 1 unidad; Cilantro al gusto</t>
+  </si>
+  <si>
+    <t>Cocinar carne y pollo con cebolla y sal; Agregar yuca y mazorca; Cocinar 20 minutos; Agregar papa y zanahoria; Cocinar 20 minutos mas; Servir con cilantro y hogao</t>
+  </si>
+  <si>
+    <t>Arroz Atollado</t>
+  </si>
+  <si>
+    <t>Arroz 300g; Costilla de cerdo 300g; Papa 2 unidad; Hogao 4 cucharadas; Color 1 cucharadita; Cilantro al gusto; Sal al gusto</t>
+  </si>
+  <si>
+    <t>Sofreir la costilla con hogao y color; Agregar el arroz y mezclar; Cubrir con agua y cocinar 15 minutos; Agregar papa en cubos; Cocinar 15 minutos mas hasta cremoso; Servir con cilantro</t>
+  </si>
+  <si>
+    <t>Sopa de Maiz</t>
+  </si>
+  <si>
+    <t>Maiz desgranado 400g; Costilla de cerdo 300g; Papa criolla 200g; Cebolla 1 unidad; Ajo 3 dientes; Cilantro al gusto; Sal al gusto</t>
+  </si>
+  <si>
+    <t>Cocinar la costilla con agua sal y cebolla; Agregar el maiz; Cocinar 30 minutos; Agregar papa criolla; Cocinar 20 minutos mas; Servir con cilantro abundante</t>
+  </si>
+  <si>
+    <t>Carne a la Llanera</t>
+  </si>
+  <si>
+    <t>Carne de res 1kg; Sal gruesa al gusto; Ajo 6 dientes; Limón 3 unidad</t>
+  </si>
+  <si>
+    <t>Limpiar la carne y hacerle cortes; Frotar con sal gruesa ajo y limon; Ensartar en vara de madera; Clavar en el suelo alrededor del fuego; Cocinar 3 horas rotando; Servir con yuca y ensalada</t>
+  </si>
+  <si>
+    <t>Sopa de Guineo</t>
+  </si>
+  <si>
+    <t>Guineo verde 4 unidad; Costilla de res 300g; Cebolla 1 unidad; Ajo 2 dientes; Cilantro al gusto; Sal al gusto</t>
+  </si>
+  <si>
+    <t>Cocinar la costilla con agua cebolla y sal; Pelar y picar los guineos; Agregar al caldo; Cocinar 25 minutos; Sazonar con ajo y cilantro; Servir caliente</t>
+  </si>
+  <si>
+    <t>Arroz con Leche</t>
+  </si>
+  <si>
+    <t>Arroz 200g; Leche 1 litro; Azucar 150g; Canela 2 astillas; Clavos 3 unidad; Limon ralladura 1 unidad</t>
+  </si>
+  <si>
+    <t>Cocinar el arroz en agua hasta suavizar; Agregar la leche y especias; Cocinar a fuego bajo revolviendo; Agregar azucar y ralladura de limon; Cocinar hasta espesar; Servir frio o caliente</t>
+  </si>
+  <si>
+    <t>Sopa de Pasta</t>
+  </si>
+  <si>
+    <t>Pasta coditos 200g; Pollo 300g; Zanahoria 1 unidad; Papa 2 unidad; Cebolla 1 unidad; Cilantro al gusto; Sal al gusto</t>
+  </si>
+  <si>
+    <t>Cocinar el pollo y desmechar; Sofreir cebolla y zanahoria; Agregar caldo de pollo; Agregar papa y cocinar 15 minutos; Agregar pasta y cocinar 10 minutos; Servir con cilantro</t>
+  </si>
+  <si>
+    <t>Frijoles con Garra</t>
+  </si>
+  <si>
+    <t>Frijoles 300g; Garra de cerdo 2 unidad; Hogao 3 cucharadas; Comino 1 cucharadita; Sal al gusto; Cilantro al gusto</t>
+  </si>
+  <si>
+    <t>Remojar frijoles la noche anterior; Cocinar frijoles con garra en olla a presion 40 minutos; Agregar hogao y comino; Cocinar 10 minutos mas; Ajustar sal; Servir con cilantro y arroz</t>
+  </si>
+  <si>
+    <t>Pollo al Disco</t>
+  </si>
+  <si>
+    <t>Pollo 800g; Papa 3 unidad; Pimenton 1 unidad; Tomate 2 unidad; Cebolla 1 unidad; Cerveza 350ml; Sal y especias al gusto</t>
+  </si>
+  <si>
+    <t>Sellar el pollo en el disco caliente; Agregar verduras picadas; Incorporar la cerveza; Agregar papa en cubos; Tapar y cocinar 30 minutos; Servir directo del disco</t>
+  </si>
+  <si>
+    <t>Sopa de Cebada</t>
+  </si>
+  <si>
+    <t>Cebada 200g; Costilla de cerdo 300g; Papa 2 unidad; Arveja 100g; Cebolla 1 unidad; Cilantro al gusto; Sal al gusto</t>
+  </si>
+  <si>
+    <t>Remojar la cebada 2 horas; Cocinar costilla con agua y sal; Agregar cebada y cebolla; Cocinar 30 minutos; Agregar papa y arveja; Cocinar 20 minutos; Servir con cilantro</t>
+  </si>
+  <si>
+    <t>Picada Colombiana</t>
+  </si>
+  <si>
+    <t>Chorizos 4 unidad; Morcilla 2 unidad; Costilla de cerdo 400g; Papa criolla 400g; Yuca 300g; Patacones 8 unidad; Hogao al gusto</t>
+  </si>
+  <si>
+    <t>Freir chorizos morcilla y costilla; Cocinar papa criolla y yuca; Freir los patacones; Servir todo en bandeja grande; Acompanar con hogao y aji</t>
+  </si>
+  <si>
+    <t>Sopa de Verduras</t>
+  </si>
+  <si>
+    <t>Zanahoria 2 unidad; Papa 2 unidad; Ahuyama 200g; Arveja 100g; Habichuelas 100g; Cebolla 1 unidad; Cilantro al gusto; Sal al gusto</t>
+  </si>
+  <si>
+    <t>Sofreir cebolla; Agregar todas las verduras picadas; Cubrir con agua; Cocinar 25 minutos; Sazonar con sal; Servir con cilantro y pan</t>
+  </si>
+  <si>
+    <t>Carne Oreada</t>
+  </si>
+  <si>
+    <t>Carne de res 600g; Sal gruesa 3 cucharadas; Ajo 4 dientes; Comino 1 cucharadita; Limon 2 unidad</t>
+  </si>
+  <si>
+    <t>Cortar la carne en laminas delgadas; Marinar con sal ajo comino y limon; Colgar al sol 24 horas; Asar a las brasas 5 minutos por lado; Servir con yuca patacones y ensalada</t>
+  </si>
+  <si>
+    <t>Sopa de Lentejas con Platano</t>
+  </si>
+  <si>
+    <t>Lentejas 250g; Platano maduro 1 unidad; Papa 2 unidad; Tomate 2 unidad; Cebolla 1 unidad; Ajo 3 dientes; Cilantro al gusto; Sal al gusto</t>
+  </si>
+  <si>
+    <t>Sofreir cebolla ajo y tomate; Agregar lentejas y cubrir con agua; Cocinar 20 minutos; Agregar papa y platano maduro; Cocinar 15 minutos mas; Servir con cilantro</t>
+  </si>
+  <si>
+    <t>Chicharron de Pollo</t>
+  </si>
+  <si>
+    <t>Pollo 600g; Harina 100g; Huevo 2 unidad; Ajo 3 dientes; Sal y pimienta al gusto; Aceite para freir</t>
+  </si>
+  <si>
+    <t>Cortar el pollo en presas; Marinar con ajo sal y pimienta; Pasar por harina luego por huevo y otra vez por harina; Freir en aceite caliente 8 minutos; Escurrir y servir con papa y hogao</t>
+  </si>
+  <si>
+    <t>Sopa de Pollo con Albahaca</t>
+  </si>
+  <si>
+    <t>Pollo 500g; Papa 3 unidad; Albahaca fresca al gusto; Cebolla 1 unidad; Ajo 2 unidad; Sal al gusto</t>
+  </si>
+  <si>
+    <t>Cocinar el pollo con cebolla ajo y sal; Desmechar el pollo; Agregar papa en cubos al caldo; Cocinar 20 minutos; Agregar albahaca fresca; Servir caliente</t>
+  </si>
+  <si>
+    <t>Fideo Gordo con Pollo</t>
+  </si>
+  <si>
+    <t>Fideo gordo 300g; Pollo 400g; Hogao 4 cucharadas; Color 1 cucharadita; Cilantro al gusto; Sal al gusto</t>
+  </si>
+  <si>
+    <t>Sofreir el pollo con hogao y color; Agregar agua y dejar hervir; Agregar los fideos; Cocinar 12 minutos; Sazonar con sal; Servir con cilantro</t>
+  </si>
+  <si>
+    <t>Conejo Guisado</t>
+  </si>
+  <si>
+    <t>Conejo 1 unidad; Tomate 3 unidad; Cebolla 1 unidad; Ajo 4 dientes; Papas 3 unidad; Cilantro al gusto; Sal y comino al gusto</t>
+  </si>
+  <si>
+    <t>Cortar el conejo en presas; Sofreir con ajo y cebolla; Agregar tomate y cocinar 10 minutos; Cubrir con agua y sazonar; Agregar papa y cocinar 30 minutos; Servir con cilantro</t>
+  </si>
+  <si>
+    <t>Locro de Papa</t>
+  </si>
+  <si>
+    <t>Papa 500g; Leche 300ml; Queso campesino 150g; Cebolla 1 unidad; Mantequilla 30g; Cilantro al gusto; Sal al gusto</t>
+  </si>
+  <si>
+    <t>Sofreir cebolla en mantequilla; Agregar papa picada; Cubrir con agua y cocinar 20 minutos; Agregar leche y queso; Cocinar 10 minutos mas; Servir con cilantro</t>
+  </si>
+  <si>
+    <t>Marranitas</t>
+  </si>
+  <si>
+    <t>Platano verde 3 unidad; Chicharron 200g; Aceite para freir; Sal al gusto</t>
+  </si>
+  <si>
+    <t>Pelar y cortar los platanos; Freir hasta dorar; Aplastar cada tajada; Colocar chicharron en el centro; Cerrar y apretar; Freir nuevamente hasta dorar; Escurrir y servir</t>
+  </si>
+  <si>
+    <t>Patacones con Hogao</t>
+  </si>
+  <si>
+    <t>Platano verde 2 unidad; Hogao 4 cucharadas; Aceite para freir; Sal al gusto</t>
+  </si>
+  <si>
+    <t>Pelar y cortar el platano en rodajas; Freir a fuego medio 5 minutos; Retirar y aplastar; Freir nuevamente hasta dorar; Escurrir; Servir con hogao encima</t>
+  </si>
+  <si>
+    <t>Chontaduro con Sal</t>
+  </si>
+  <si>
+    <t>Chontaduro 500g; Sal al gusto; Miel opcional</t>
+  </si>
+  <si>
+    <t>Cocinar el chontaduro en agua con sal 20 minutos; Escurrir y pelar; Servir con sal o miel al gusto; Acompanar con agua de panela</t>
+  </si>
+  <si>
+    <t>Cocadas</t>
+  </si>
+  <si>
+    <t>Coco rallado 300g; Azucar 200g; Leche de coco 100ml; Canela al gusto</t>
+  </si>
+  <si>
+    <t>Mezclar coco rallado con azucar y leche de coco; Agregar canela; Cocinar a fuego bajo revolviendo; Cuando espese retirar del fuego; Formar bolitas o cuadros; Dejar enfriar</t>
+  </si>
+  <si>
+    <t>Alegrías de Maiz</t>
+  </si>
+  <si>
+    <t>Maiz pira reventado 200g; Panela 150g; Agua 50ml; Anis al gusto</t>
+  </si>
+  <si>
+    <t>Hacer melado con panela agua y anis; Mezclar con el maiz reventado; Formar bolitas rapidamente antes de enfriar; Dejar solidificar; Envolver en papel</t>
+  </si>
+  <si>
+    <t>Manjar Blanco</t>
+  </si>
+  <si>
+    <t>Leche 2 litros; Azucar 300g; Maizena 50g; Canela 1 astilla</t>
+  </si>
+  <si>
+    <t>Disolver maizena en leche fria; Agregar azucar y canela; Cocinar a fuego bajo revolviendo constantemente; Cocinar hasta que la mezcla se despegue de la olla; Verter en molde; Dejar enfriar</t>
+  </si>
+  <si>
+    <t>Almojabanas</t>
+  </si>
+  <si>
+    <t>Cuajada 300g; Harina de maiz 200g; Huevo 2 unidad; Sal 1 cucharadita; Azucar 1 cucharadita</t>
+  </si>
+  <si>
+    <t>Desmenuzar la cuajada; Mezclar con harina huevos sal y azucar; Amasar hasta obtener masa suave; Formar bolitas; Hornear a 180 grados 20 minutos; Servir calientes</t>
+  </si>
+  <si>
+    <t>Insulsos</t>
+  </si>
+  <si>
+    <t>Maiz 300g; Panela 100g; Anís 1 cucharadita; Agua al gusto</t>
+  </si>
+  <si>
+    <t>Tostar el maiz en sarten sin aceite; Moler el maiz tostado; Hacer melado con panela y anis; Mezclar con el maiz molido; Formar bollitos pequenos; Dejar enfriar</t>
+  </si>
+  <si>
+    <t>Caballeros Pobres</t>
+  </si>
+  <si>
+    <t>Pan tajado 8 tajadas; Huevo 3 unidad; Leche 100ml; Azucar 2 cucharadas; Canela al gusto; Aceite para freir</t>
+  </si>
+  <si>
+    <t>Batir huevos con leche; Remojar el pan en la mezcla; Freir en aceite caliente; Escurrir; Espolvorear azucar y canela; Servir caliente con arequipe</t>
+  </si>
+  <si>
+    <t>Mazamorra Chiquita</t>
+  </si>
+  <si>
+    <t>Maiz trillado 300g; Leche 500ml; Panela 100g; Sal al gusto</t>
+  </si>
+  <si>
+    <t>Cocinar el maiz trillado en agua hasta suavizar; Agregar leche; Cocinar 10 minutos mas; Agregar panela o sal segun preferencia; Servir caliente en taza</t>
+  </si>
+  <si>
+    <t>Gelatina de Pata</t>
+  </si>
+  <si>
+    <t>Pata de res 1 unidad; Panela 200g; Canela 2 astillas; Clavos 4 unidad; Limon 2 unidad</t>
+  </si>
+  <si>
+    <t>Cocinar la pata con agua 2 horas hasta obtener caldo gelatinoso; Colar el caldo; Agregar panela canela y clavos; Hervir 15 minutos; Agregar limon; Verter en moldes y refrigerar</t>
+  </si>
+  <si>
+    <t>Torta de Platano</t>
+  </si>
+  <si>
+    <t>Platano maduro 4 unidad; Huevos 3 unidad; Azucar 100g; Mantequilla 50g; Harina 100g; Polvo de hornear 1 cucharadita</t>
+  </si>
+  <si>
+    <t>Machacar los platanos maduros; Mezclar con huevos azucar y mantequilla; Agregar harina y polvo de hornear; Verter en molde engrasado; Hornear a 180 grados 35 minutos</t>
+  </si>
+  <si>
+    <t>Brazo de Reina</t>
+  </si>
+  <si>
+    <t>Harina 200g; Huevos 4 unidad; Azucar 150g; Arequipe 300g; Coco rallado 100g</t>
+  </si>
+  <si>
+    <t>Batir huevos con azucar hasta esponjar; Incorporar harina; Hornear en bandeja plana 15 minutos; Desmoldar sobre trapo humedo; Rellenar con arequipe; Enrollar y cubrir con coco rallado</t>
+  </si>
+  <si>
+    <t>Suspiros</t>
+  </si>
+  <si>
+    <t>Claras de huevo 4 unidad; Azucar 200g; Limon unas gotas; Colorante opcional</t>
+  </si>
+  <si>
+    <t>Batir las claras a punto de nieve; Agregar azucar poco a poco; Agregar limon; Poner en manga pastelera; Hornear a 100 grados 60 minutos; Dejar enfriar en el horno</t>
+  </si>
+  <si>
+    <t>Torta de Choclo</t>
+  </si>
+  <si>
+    <t>Maiz tierno 6 mazorcas; Huevos 3 unidad; Mantequilla 80g; Azucar 100g; Sal 1 cucharadita; Queso campesino 150g</t>
+  </si>
+  <si>
+    <t>Desgranar y licuar el maiz; Mezclar con huevos mantequilla azucar y sal; Agregar queso desmenuzado; Verter en molde engrasado; Hornear a 180 grados 40 minutos; Servir tibio</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/arepas_ahogao_ke677p</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Arepas_de_Choclo_Rellenas_whznzb</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Caldo_de_Huevo_p4wxcz</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Mogolla_con_Queso_ffeii5</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Natilla_con_Buneulos_zblho0</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/hervido_de_furtas_gjgyhu</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Arepa_de_Maiz_Pelao_g1lc1x</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Masato_de_Arroz_o98mxs</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Obleas_con_Arequipe_pr1ifm</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Sancocho_de_Pescado_vrt2da</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Aguapanela_con_Queso_yeufxe</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Tamales_de_Pipian_dzk8sl</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Crispetas_de_Maiz_ee4jk7</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Colada_de_Avena_bdisxv</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Arepas_de_Pipian_wie7f8</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Viudo_de_Pescado_mcedk5</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Pepitoria_de_Cabro_rue7nh</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Cocido_Boyacense_xmlrjv</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Lengua_en_Salsa_esy1jb</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Arroz_de_Coco_con_Mariscos_okrjch</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Cuchuco_de_Trigo_c5c41o</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Sopa_de_Tortilla_i0sxds</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Estofado_de_Res_c93gb5</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Chuleta_Valle_ywafqj</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Sopa_de_Ahuyama_pafffd</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Mojarra_Frita_sieckl</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Puchero_Bogotano_cxyvcf</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Arroz_Atollado_wuh3c2</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Sopa_de_Maiz_qnvlx7</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Carne_a_la_Llanera_uomhwm</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Sopa_de_Guineo_b5c4n6</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Arroz_con_Leche_ohs4at</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Sopa_de_Pasta_zvocak</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Frijoles_con_Garra_alh6kz</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Pollo_al_Disco_t5y8qv</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Sopa_de_Cebada_txguiq</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Picada_Colombiana_kqbwer</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Sopa_de_Verduras_q0tswf</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Carne_Oreada_ol1cpv</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Sopa_de_Lentejas_con_Platano_zzxami</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Chicharron_de_Pollo_wi0ubw</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Sopa_de_Pollo_con_Albahaca_bfcj7t</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Fideo_Gordo_con_Pollo_vthbgi</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Conejo_Guisado_a329ov</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Locro_de_Papa_ptofqh</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Marranitas_hdqzdc</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Patacones_con_Hogao_h3zmyt</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Chontaduro_con_Sal_tfp68t</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Cocadas_kkfvil</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Alegrías_de_Maiz_wg2ky8</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Manjar_Blanco_asxkbq</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Almojabanas_e8oyca</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Insulsos_etep1g</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Caballeros_Pobres_zbbpjs</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Mazamorra_Chiquita_cnitnx</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Gelatina_de_Pata_yrv6bm</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Torta_de_Choclo_toynpc</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Brazo_de_Reina_a1sv0s</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Suspiros_vxd6j1</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dcvctj3rw/image/upload/Torta_de_Choclo_ezjzry</t>
   </si>
 </sst>
 </file>
@@ -735,7 +1455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.28515625" bestFit="1" customWidth="1"/>
@@ -1199,18 +1919,18 @@
         <v>2</v>
       </c>
       <c r="J12" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="K12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -1237,18 +1957,18 @@
         <v>2</v>
       </c>
       <c r="J13" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="K13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -1275,18 +1995,18 @@
         <v>6</v>
       </c>
       <c r="J14" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="K14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L14" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -1313,18 +2033,18 @@
         <v>6</v>
       </c>
       <c r="J15" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="K15" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="L15" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
         <v>27</v>
@@ -1351,18 +2071,18 @@
         <v>6</v>
       </c>
       <c r="J16" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="K16" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L16" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B17" t="s">
         <v>27</v>
@@ -1389,18 +2109,18 @@
         <v>6</v>
       </c>
       <c r="J17" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="K17" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="L17" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
@@ -1427,18 +2147,18 @@
         <v>4</v>
       </c>
       <c r="J18" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="K18" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L18" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
         <v>27</v>
@@ -1465,18 +2185,18 @@
         <v>4</v>
       </c>
       <c r="J19" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="K19" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="L19" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B20" t="s">
         <v>42</v>
@@ -1503,18 +2223,18 @@
         <v>4</v>
       </c>
       <c r="J20" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="K20" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="L20" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B21" t="s">
         <v>42</v>
@@ -1541,18 +2261,18 @@
         <v>4</v>
       </c>
       <c r="J21" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="K21" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="L21" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B22" t="s">
         <v>42</v>
@@ -1579,18 +2299,18 @@
         <v>6</v>
       </c>
       <c r="J22" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="K22" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="L22" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="B23" t="s">
         <v>42</v>
@@ -1617,18 +2337,18 @@
         <v>4</v>
       </c>
       <c r="J23" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="K23" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="L23" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="B24" t="s">
         <v>51</v>
@@ -1655,18 +2375,18 @@
         <v>4</v>
       </c>
       <c r="J24" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="K24" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="L24" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="B25" t="s">
         <v>51</v>
@@ -1693,18 +2413,18 @@
         <v>4</v>
       </c>
       <c r="J25" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="K25" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="L25" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="B26" t="s">
         <v>51</v>
@@ -1731,13 +2451,2293 @@
         <v>10</v>
       </c>
       <c r="J26" t="s">
+        <v>116</v>
+      </c>
+      <c r="K26" t="s">
+        <v>117</v>
+      </c>
+      <c r="L26" t="s">
         <v>118</v>
       </c>
-      <c r="K26" t="s">
-        <v>101</v>
-      </c>
-      <c r="L26" t="s">
-        <v>102</v>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27">
+        <v>320</v>
+      </c>
+      <c r="D27">
+        <v>8</v>
+      </c>
+      <c r="E27">
+        <v>48</v>
+      </c>
+      <c r="F27">
+        <v>10</v>
+      </c>
+      <c r="G27">
+        <v>20</v>
+      </c>
+      <c r="H27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27">
+        <v>4</v>
+      </c>
+      <c r="J27" t="s">
+        <v>299</v>
+      </c>
+      <c r="K27" t="s">
+        <v>120</v>
+      </c>
+      <c r="L27" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28">
+        <v>380</v>
+      </c>
+      <c r="D28">
+        <v>12</v>
+      </c>
+      <c r="E28">
+        <v>46</v>
+      </c>
+      <c r="F28">
+        <v>16</v>
+      </c>
+      <c r="G28">
+        <v>35</v>
+      </c>
+      <c r="H28" t="s">
+        <v>33</v>
+      </c>
+      <c r="I28">
+        <v>4</v>
+      </c>
+      <c r="J28" t="s">
+        <v>300</v>
+      </c>
+      <c r="K28" t="s">
+        <v>123</v>
+      </c>
+      <c r="L28" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29">
+        <v>160</v>
+      </c>
+      <c r="D29">
+        <v>10</v>
+      </c>
+      <c r="E29">
+        <v>8</v>
+      </c>
+      <c r="F29">
+        <v>10</v>
+      </c>
+      <c r="G29">
+        <v>15</v>
+      </c>
+      <c r="H29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29">
+        <v>2</v>
+      </c>
+      <c r="J29" t="s">
+        <v>301</v>
+      </c>
+      <c r="K29" t="s">
+        <v>126</v>
+      </c>
+      <c r="L29" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30">
+        <v>290</v>
+      </c>
+      <c r="D30">
+        <v>10</v>
+      </c>
+      <c r="E30">
+        <v>42</v>
+      </c>
+      <c r="F30">
+        <v>8</v>
+      </c>
+      <c r="G30">
+        <v>10</v>
+      </c>
+      <c r="H30" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="J30" t="s">
+        <v>302</v>
+      </c>
+      <c r="K30" t="s">
+        <v>129</v>
+      </c>
+      <c r="L30" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>131</v>
+      </c>
+      <c r="B31" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31">
+        <v>420</v>
+      </c>
+      <c r="D31">
+        <v>8</v>
+      </c>
+      <c r="E31">
+        <v>68</v>
+      </c>
+      <c r="F31">
+        <v>14</v>
+      </c>
+      <c r="G31">
+        <v>60</v>
+      </c>
+      <c r="H31" t="s">
+        <v>33</v>
+      </c>
+      <c r="I31">
+        <v>6</v>
+      </c>
+      <c r="J31" t="s">
+        <v>303</v>
+      </c>
+      <c r="K31" t="s">
+        <v>132</v>
+      </c>
+      <c r="L31" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>134</v>
+      </c>
+      <c r="B32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32">
+        <v>180</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32">
+        <v>42</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>20</v>
+      </c>
+      <c r="H32" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32">
+        <v>4</v>
+      </c>
+      <c r="J32" t="s">
+        <v>304</v>
+      </c>
+      <c r="K32" t="s">
+        <v>135</v>
+      </c>
+      <c r="L32" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>137</v>
+      </c>
+      <c r="B33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33">
+        <v>280</v>
+      </c>
+      <c r="D33">
+        <v>6</v>
+      </c>
+      <c r="E33">
+        <v>52</v>
+      </c>
+      <c r="F33">
+        <v>5</v>
+      </c>
+      <c r="G33">
+        <v>30</v>
+      </c>
+      <c r="H33" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33">
+        <v>6</v>
+      </c>
+      <c r="J33" t="s">
+        <v>305</v>
+      </c>
+      <c r="K33" t="s">
+        <v>138</v>
+      </c>
+      <c r="L33" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>140</v>
+      </c>
+      <c r="B34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34">
+        <v>220</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34">
+        <v>48</v>
+      </c>
+      <c r="F34">
+        <v>2</v>
+      </c>
+      <c r="G34">
+        <v>30</v>
+      </c>
+      <c r="H34" t="s">
+        <v>14</v>
+      </c>
+      <c r="I34">
+        <v>6</v>
+      </c>
+      <c r="J34" t="s">
+        <v>306</v>
+      </c>
+      <c r="K34" t="s">
+        <v>141</v>
+      </c>
+      <c r="L34" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>143</v>
+      </c>
+      <c r="B35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35">
+        <v>310</v>
+      </c>
+      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35">
+        <v>58</v>
+      </c>
+      <c r="F35">
+        <v>7</v>
+      </c>
+      <c r="G35">
+        <v>10</v>
+      </c>
+      <c r="H35" t="s">
+        <v>14</v>
+      </c>
+      <c r="I35">
+        <v>4</v>
+      </c>
+      <c r="J35" t="s">
+        <v>307</v>
+      </c>
+      <c r="K35" t="s">
+        <v>144</v>
+      </c>
+      <c r="L35" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>146</v>
+      </c>
+      <c r="B36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36">
+        <v>340</v>
+      </c>
+      <c r="D36">
+        <v>28</v>
+      </c>
+      <c r="E36">
+        <v>32</v>
+      </c>
+      <c r="F36">
+        <v>10</v>
+      </c>
+      <c r="G36">
+        <v>45</v>
+      </c>
+      <c r="H36" t="s">
+        <v>33</v>
+      </c>
+      <c r="I36">
+        <v>4</v>
+      </c>
+      <c r="J36" t="s">
+        <v>308</v>
+      </c>
+      <c r="K36" t="s">
+        <v>147</v>
+      </c>
+      <c r="L36" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>149</v>
+      </c>
+      <c r="B37" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37">
+        <v>240</v>
+      </c>
+      <c r="D37">
+        <v>8</v>
+      </c>
+      <c r="E37">
+        <v>44</v>
+      </c>
+      <c r="F37">
+        <v>5</v>
+      </c>
+      <c r="G37">
+        <v>10</v>
+      </c>
+      <c r="H37" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37">
+        <v>2</v>
+      </c>
+      <c r="J37" t="s">
+        <v>309</v>
+      </c>
+      <c r="K37" t="s">
+        <v>150</v>
+      </c>
+      <c r="L37" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>152</v>
+      </c>
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38">
+        <v>460</v>
+      </c>
+      <c r="D38">
+        <v>18</v>
+      </c>
+      <c r="E38">
+        <v>62</v>
+      </c>
+      <c r="F38">
+        <v>16</v>
+      </c>
+      <c r="G38">
+        <v>90</v>
+      </c>
+      <c r="H38" t="s">
+        <v>28</v>
+      </c>
+      <c r="I38">
+        <v>8</v>
+      </c>
+      <c r="J38" t="s">
+        <v>310</v>
+      </c>
+      <c r="K38" t="s">
+        <v>153</v>
+      </c>
+      <c r="L38" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>155</v>
+      </c>
+      <c r="B39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39">
+        <v>150</v>
+      </c>
+      <c r="D39">
+        <v>3</v>
+      </c>
+      <c r="E39">
+        <v>28</v>
+      </c>
+      <c r="F39">
+        <v>4</v>
+      </c>
+      <c r="G39">
+        <v>10</v>
+      </c>
+      <c r="H39" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39">
+        <v>4</v>
+      </c>
+      <c r="J39" t="s">
+        <v>311</v>
+      </c>
+      <c r="K39" t="s">
+        <v>156</v>
+      </c>
+      <c r="L39" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>158</v>
+      </c>
+      <c r="B40" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40">
+        <v>260</v>
+      </c>
+      <c r="D40">
+        <v>6</v>
+      </c>
+      <c r="E40">
+        <v>48</v>
+      </c>
+      <c r="F40">
+        <v>5</v>
+      </c>
+      <c r="G40">
+        <v>15</v>
+      </c>
+      <c r="H40" t="s">
+        <v>14</v>
+      </c>
+      <c r="I40">
+        <v>4</v>
+      </c>
+      <c r="J40" t="s">
+        <v>312</v>
+      </c>
+      <c r="K40" t="s">
+        <v>159</v>
+      </c>
+      <c r="L40" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>161</v>
+      </c>
+      <c r="B41" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41">
+        <v>300</v>
+      </c>
+      <c r="D41">
+        <v>9</v>
+      </c>
+      <c r="E41">
+        <v>44</v>
+      </c>
+      <c r="F41">
+        <v>10</v>
+      </c>
+      <c r="G41">
+        <v>40</v>
+      </c>
+      <c r="H41" t="s">
+        <v>33</v>
+      </c>
+      <c r="I41">
+        <v>6</v>
+      </c>
+      <c r="J41" t="s">
+        <v>313</v>
+      </c>
+      <c r="K41" t="s">
+        <v>162</v>
+      </c>
+      <c r="L41" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>164</v>
+      </c>
+      <c r="B42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42">
+        <v>480</v>
+      </c>
+      <c r="D42">
+        <v>36</v>
+      </c>
+      <c r="E42">
+        <v>48</v>
+      </c>
+      <c r="F42">
+        <v>12</v>
+      </c>
+      <c r="G42">
+        <v>60</v>
+      </c>
+      <c r="H42" t="s">
+        <v>33</v>
+      </c>
+      <c r="I42">
+        <v>4</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="K42" t="s">
+        <v>165</v>
+      </c>
+      <c r="L42" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>167</v>
+      </c>
+      <c r="B43" t="s">
+        <v>27</v>
+      </c>
+      <c r="C43">
+        <v>520</v>
+      </c>
+      <c r="D43">
+        <v>38</v>
+      </c>
+      <c r="E43">
+        <v>28</v>
+      </c>
+      <c r="F43">
+        <v>24</v>
+      </c>
+      <c r="G43">
+        <v>90</v>
+      </c>
+      <c r="H43" t="s">
+        <v>28</v>
+      </c>
+      <c r="I43">
+        <v>6</v>
+      </c>
+      <c r="J43" t="s">
+        <v>315</v>
+      </c>
+      <c r="K43" t="s">
+        <v>168</v>
+      </c>
+      <c r="L43" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>170</v>
+      </c>
+      <c r="B44" t="s">
+        <v>27</v>
+      </c>
+      <c r="C44">
+        <v>560</v>
+      </c>
+      <c r="D44">
+        <v>32</v>
+      </c>
+      <c r="E44">
+        <v>68</v>
+      </c>
+      <c r="F44">
+        <v>14</v>
+      </c>
+      <c r="G44">
+        <v>90</v>
+      </c>
+      <c r="H44" t="s">
+        <v>33</v>
+      </c>
+      <c r="I44">
+        <v>6</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="K44" t="s">
+        <v>171</v>
+      </c>
+      <c r="L44" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>173</v>
+      </c>
+      <c r="B45" t="s">
+        <v>27</v>
+      </c>
+      <c r="C45">
+        <v>540</v>
+      </c>
+      <c r="D45">
+        <v>44</v>
+      </c>
+      <c r="E45">
+        <v>18</v>
+      </c>
+      <c r="F45">
+        <v>26</v>
+      </c>
+      <c r="G45">
+        <v>150</v>
+      </c>
+      <c r="H45" t="s">
+        <v>28</v>
+      </c>
+      <c r="I45">
+        <v>6</v>
+      </c>
+      <c r="J45" t="s">
+        <v>317</v>
+      </c>
+      <c r="K45" t="s">
+        <v>174</v>
+      </c>
+      <c r="L45" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>176</v>
+      </c>
+      <c r="B46" t="s">
+        <v>27</v>
+      </c>
+      <c r="C46">
+        <v>580</v>
+      </c>
+      <c r="D46">
+        <v>32</v>
+      </c>
+      <c r="E46">
+        <v>72</v>
+      </c>
+      <c r="F46">
+        <v>18</v>
+      </c>
+      <c r="G46">
+        <v>45</v>
+      </c>
+      <c r="H46" t="s">
+        <v>33</v>
+      </c>
+      <c r="I46">
+        <v>4</v>
+      </c>
+      <c r="J46" t="s">
+        <v>318</v>
+      </c>
+      <c r="K46" t="s">
+        <v>177</v>
+      </c>
+      <c r="L46" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>179</v>
+      </c>
+      <c r="B47" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47">
+        <v>440</v>
+      </c>
+      <c r="D47">
+        <v>24</v>
+      </c>
+      <c r="E47">
+        <v>58</v>
+      </c>
+      <c r="F47">
+        <v>12</v>
+      </c>
+      <c r="G47">
+        <v>75</v>
+      </c>
+      <c r="H47" t="s">
+        <v>33</v>
+      </c>
+      <c r="I47">
+        <v>6</v>
+      </c>
+      <c r="J47" t="s">
+        <v>319</v>
+      </c>
+      <c r="K47" t="s">
+        <v>180</v>
+      </c>
+      <c r="L47" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>182</v>
+      </c>
+      <c r="B48" t="s">
+        <v>27</v>
+      </c>
+      <c r="C48">
+        <v>380</v>
+      </c>
+      <c r="D48">
+        <v>16</v>
+      </c>
+      <c r="E48">
+        <v>52</v>
+      </c>
+      <c r="F48">
+        <v>12</v>
+      </c>
+      <c r="G48">
+        <v>40</v>
+      </c>
+      <c r="H48" t="s">
+        <v>14</v>
+      </c>
+      <c r="I48">
+        <v>4</v>
+      </c>
+      <c r="J48" t="s">
+        <v>320</v>
+      </c>
+      <c r="K48" t="s">
+        <v>183</v>
+      </c>
+      <c r="L48" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>185</v>
+      </c>
+      <c r="B49" t="s">
+        <v>27</v>
+      </c>
+      <c r="C49">
+        <v>520</v>
+      </c>
+      <c r="D49">
+        <v>40</v>
+      </c>
+      <c r="E49">
+        <v>32</v>
+      </c>
+      <c r="F49">
+        <v>20</v>
+      </c>
+      <c r="G49">
+        <v>90</v>
+      </c>
+      <c r="H49" t="s">
+        <v>33</v>
+      </c>
+      <c r="I49">
+        <v>4</v>
+      </c>
+      <c r="J49" t="s">
+        <v>321</v>
+      </c>
+      <c r="K49" t="s">
+        <v>186</v>
+      </c>
+      <c r="L49" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>188</v>
+      </c>
+      <c r="B50" t="s">
+        <v>27</v>
+      </c>
+      <c r="C50">
+        <v>480</v>
+      </c>
+      <c r="D50">
+        <v>42</v>
+      </c>
+      <c r="E50">
+        <v>8</v>
+      </c>
+      <c r="F50">
+        <v>28</v>
+      </c>
+      <c r="G50">
+        <v>30</v>
+      </c>
+      <c r="H50" t="s">
+        <v>14</v>
+      </c>
+      <c r="I50">
+        <v>2</v>
+      </c>
+      <c r="J50" t="s">
+        <v>322</v>
+      </c>
+      <c r="K50" t="s">
+        <v>189</v>
+      </c>
+      <c r="L50" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>191</v>
+      </c>
+      <c r="B51" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51">
+        <v>280</v>
+      </c>
+      <c r="D51">
+        <v>8</v>
+      </c>
+      <c r="E51">
+        <v>42</v>
+      </c>
+      <c r="F51">
+        <v>8</v>
+      </c>
+      <c r="G51">
+        <v>35</v>
+      </c>
+      <c r="H51" t="s">
+        <v>14</v>
+      </c>
+      <c r="I51">
+        <v>4</v>
+      </c>
+      <c r="J51" t="s">
+        <v>323</v>
+      </c>
+      <c r="K51" t="s">
+        <v>192</v>
+      </c>
+      <c r="L51" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>194</v>
+      </c>
+      <c r="B52" t="s">
+        <v>27</v>
+      </c>
+      <c r="C52">
+        <v>420</v>
+      </c>
+      <c r="D52">
+        <v>44</v>
+      </c>
+      <c r="E52">
+        <v>12</v>
+      </c>
+      <c r="F52">
+        <v>22</v>
+      </c>
+      <c r="G52">
+        <v>25</v>
+      </c>
+      <c r="H52" t="s">
+        <v>14</v>
+      </c>
+      <c r="I52">
+        <v>2</v>
+      </c>
+      <c r="J52" t="s">
+        <v>324</v>
+      </c>
+      <c r="K52" t="s">
+        <v>195</v>
+      </c>
+      <c r="L52" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>197</v>
+      </c>
+      <c r="B53" t="s">
+        <v>27</v>
+      </c>
+      <c r="C53">
+        <v>560</v>
+      </c>
+      <c r="D53">
+        <v>36</v>
+      </c>
+      <c r="E53">
+        <v>58</v>
+      </c>
+      <c r="F53">
+        <v>16</v>
+      </c>
+      <c r="G53">
+        <v>90</v>
+      </c>
+      <c r="H53" t="s">
+        <v>33</v>
+      </c>
+      <c r="I53">
+        <v>6</v>
+      </c>
+      <c r="J53" t="s">
+        <v>325</v>
+      </c>
+      <c r="K53" t="s">
+        <v>198</v>
+      </c>
+      <c r="L53" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>200</v>
+      </c>
+      <c r="B54" t="s">
+        <v>27</v>
+      </c>
+      <c r="C54">
+        <v>520</v>
+      </c>
+      <c r="D54">
+        <v>28</v>
+      </c>
+      <c r="E54">
+        <v>62</v>
+      </c>
+      <c r="F54">
+        <v>16</v>
+      </c>
+      <c r="G54">
+        <v>50</v>
+      </c>
+      <c r="H54" t="s">
+        <v>33</v>
+      </c>
+      <c r="I54">
+        <v>4</v>
+      </c>
+      <c r="J54" t="s">
+        <v>326</v>
+      </c>
+      <c r="K54" t="s">
+        <v>201</v>
+      </c>
+      <c r="L54" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>203</v>
+      </c>
+      <c r="B55" t="s">
+        <v>27</v>
+      </c>
+      <c r="C55">
+        <v>360</v>
+      </c>
+      <c r="D55">
+        <v>18</v>
+      </c>
+      <c r="E55">
+        <v>52</v>
+      </c>
+      <c r="F55">
+        <v>8</v>
+      </c>
+      <c r="G55">
+        <v>60</v>
+      </c>
+      <c r="H55" t="s">
+        <v>14</v>
+      </c>
+      <c r="I55">
+        <v>6</v>
+      </c>
+      <c r="J55" t="s">
+        <v>327</v>
+      </c>
+      <c r="K55" t="s">
+        <v>204</v>
+      </c>
+      <c r="L55" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>206</v>
+      </c>
+      <c r="B56" t="s">
+        <v>27</v>
+      </c>
+      <c r="C56">
+        <v>580</v>
+      </c>
+      <c r="D56">
+        <v>52</v>
+      </c>
+      <c r="E56">
+        <v>4</v>
+      </c>
+      <c r="F56">
+        <v>36</v>
+      </c>
+      <c r="G56">
+        <v>180</v>
+      </c>
+      <c r="H56" t="s">
+        <v>28</v>
+      </c>
+      <c r="I56">
+        <v>6</v>
+      </c>
+      <c r="J56" t="s">
+        <v>328</v>
+      </c>
+      <c r="K56" t="s">
+        <v>207</v>
+      </c>
+      <c r="L56" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>209</v>
+      </c>
+      <c r="B57" t="s">
+        <v>42</v>
+      </c>
+      <c r="C57">
+        <v>280</v>
+      </c>
+      <c r="D57">
+        <v>8</v>
+      </c>
+      <c r="E57">
+        <v>48</v>
+      </c>
+      <c r="F57">
+        <v>6</v>
+      </c>
+      <c r="G57">
+        <v>40</v>
+      </c>
+      <c r="H57" t="s">
+        <v>14</v>
+      </c>
+      <c r="I57">
+        <v>4</v>
+      </c>
+      <c r="J57" t="s">
+        <v>329</v>
+      </c>
+      <c r="K57" t="s">
+        <v>210</v>
+      </c>
+      <c r="L57" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>212</v>
+      </c>
+      <c r="B58" t="s">
+        <v>42</v>
+      </c>
+      <c r="C58">
+        <v>320</v>
+      </c>
+      <c r="D58">
+        <v>7</v>
+      </c>
+      <c r="E58">
+        <v>58</v>
+      </c>
+      <c r="F58">
+        <v>7</v>
+      </c>
+      <c r="G58">
+        <v>30</v>
+      </c>
+      <c r="H58" t="s">
+        <v>14</v>
+      </c>
+      <c r="I58">
+        <v>6</v>
+      </c>
+      <c r="J58" t="s">
+        <v>330</v>
+      </c>
+      <c r="K58" t="s">
+        <v>213</v>
+      </c>
+      <c r="L58" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>215</v>
+      </c>
+      <c r="B59" t="s">
+        <v>42</v>
+      </c>
+      <c r="C59">
+        <v>340</v>
+      </c>
+      <c r="D59">
+        <v>14</v>
+      </c>
+      <c r="E59">
+        <v>54</v>
+      </c>
+      <c r="F59">
+        <v>8</v>
+      </c>
+      <c r="G59">
+        <v>30</v>
+      </c>
+      <c r="H59" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59">
+        <v>4</v>
+      </c>
+      <c r="J59" t="s">
+        <v>331</v>
+      </c>
+      <c r="K59" t="s">
+        <v>216</v>
+      </c>
+      <c r="L59" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>218</v>
+      </c>
+      <c r="B60" t="s">
+        <v>42</v>
+      </c>
+      <c r="C60">
+        <v>440</v>
+      </c>
+      <c r="D60">
+        <v>28</v>
+      </c>
+      <c r="E60">
+        <v>52</v>
+      </c>
+      <c r="F60">
+        <v>14</v>
+      </c>
+      <c r="G60">
+        <v>90</v>
+      </c>
+      <c r="H60" t="s">
+        <v>33</v>
+      </c>
+      <c r="I60">
+        <v>4</v>
+      </c>
+      <c r="J60" t="s">
+        <v>332</v>
+      </c>
+      <c r="K60" t="s">
+        <v>219</v>
+      </c>
+      <c r="L60" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>221</v>
+      </c>
+      <c r="B61" t="s">
+        <v>42</v>
+      </c>
+      <c r="C61">
+        <v>480</v>
+      </c>
+      <c r="D61">
+        <v>42</v>
+      </c>
+      <c r="E61">
+        <v>18</v>
+      </c>
+      <c r="F61">
+        <v>24</v>
+      </c>
+      <c r="G61">
+        <v>45</v>
+      </c>
+      <c r="H61" t="s">
+        <v>33</v>
+      </c>
+      <c r="I61">
+        <v>4</v>
+      </c>
+      <c r="J61" t="s">
+        <v>333</v>
+      </c>
+      <c r="K61" t="s">
+        <v>222</v>
+      </c>
+      <c r="L61" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>224</v>
+      </c>
+      <c r="B62" t="s">
+        <v>42</v>
+      </c>
+      <c r="C62">
+        <v>300</v>
+      </c>
+      <c r="D62">
+        <v>12</v>
+      </c>
+      <c r="E62">
+        <v>52</v>
+      </c>
+      <c r="F62">
+        <v>6</v>
+      </c>
+      <c r="G62">
+        <v>50</v>
+      </c>
+      <c r="H62" t="s">
+        <v>14</v>
+      </c>
+      <c r="I62">
+        <v>6</v>
+      </c>
+      <c r="J62" t="s">
+        <v>334</v>
+      </c>
+      <c r="K62" t="s">
+        <v>225</v>
+      </c>
+      <c r="L62" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>227</v>
+      </c>
+      <c r="B63" t="s">
+        <v>42</v>
+      </c>
+      <c r="C63">
+        <v>620</v>
+      </c>
+      <c r="D63">
+        <v>38</v>
+      </c>
+      <c r="E63">
+        <v>28</v>
+      </c>
+      <c r="F63">
+        <v>36</v>
+      </c>
+      <c r="G63">
+        <v>40</v>
+      </c>
+      <c r="H63" t="s">
+        <v>14</v>
+      </c>
+      <c r="I63">
+        <v>4</v>
+      </c>
+      <c r="J63" t="s">
+        <v>335</v>
+      </c>
+      <c r="K63" t="s">
+        <v>228</v>
+      </c>
+      <c r="L63" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>230</v>
+      </c>
+      <c r="B64" t="s">
+        <v>42</v>
+      </c>
+      <c r="C64">
+        <v>240</v>
+      </c>
+      <c r="D64">
+        <v>8</v>
+      </c>
+      <c r="E64">
+        <v>38</v>
+      </c>
+      <c r="F64">
+        <v>6</v>
+      </c>
+      <c r="G64">
+        <v>35</v>
+      </c>
+      <c r="H64" t="s">
+        <v>14</v>
+      </c>
+      <c r="I64">
+        <v>4</v>
+      </c>
+      <c r="J64" t="s">
+        <v>336</v>
+      </c>
+      <c r="K64" t="s">
+        <v>231</v>
+      </c>
+      <c r="L64" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>233</v>
+      </c>
+      <c r="B65" t="s">
+        <v>42</v>
+      </c>
+      <c r="C65">
+        <v>460</v>
+      </c>
+      <c r="D65">
+        <v>48</v>
+      </c>
+      <c r="E65">
+        <v>4</v>
+      </c>
+      <c r="F65">
+        <v>26</v>
+      </c>
+      <c r="G65">
+        <v>1440</v>
+      </c>
+      <c r="H65" t="s">
+        <v>33</v>
+      </c>
+      <c r="I65">
+        <v>4</v>
+      </c>
+      <c r="J65" t="s">
+        <v>337</v>
+      </c>
+      <c r="K65" t="s">
+        <v>234</v>
+      </c>
+      <c r="L65" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>236</v>
+      </c>
+      <c r="B66" t="s">
+        <v>42</v>
+      </c>
+      <c r="C66">
+        <v>360</v>
+      </c>
+      <c r="D66">
+        <v>16</v>
+      </c>
+      <c r="E66">
+        <v>56</v>
+      </c>
+      <c r="F66">
+        <v>8</v>
+      </c>
+      <c r="G66">
+        <v>45</v>
+      </c>
+      <c r="H66" t="s">
+        <v>14</v>
+      </c>
+      <c r="I66">
+        <v>4</v>
+      </c>
+      <c r="J66" t="s">
+        <v>338</v>
+      </c>
+      <c r="K66" t="s">
+        <v>237</v>
+      </c>
+      <c r="L66" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>239</v>
+      </c>
+      <c r="B67" t="s">
+        <v>42</v>
+      </c>
+      <c r="C67">
+        <v>420</v>
+      </c>
+      <c r="D67">
+        <v>36</v>
+      </c>
+      <c r="E67">
+        <v>22</v>
+      </c>
+      <c r="F67">
+        <v>22</v>
+      </c>
+      <c r="G67">
+        <v>30</v>
+      </c>
+      <c r="H67" t="s">
+        <v>14</v>
+      </c>
+      <c r="I67">
+        <v>4</v>
+      </c>
+      <c r="J67" t="s">
+        <v>339</v>
+      </c>
+      <c r="K67" t="s">
+        <v>240</v>
+      </c>
+      <c r="L67" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>242</v>
+      </c>
+      <c r="B68" t="s">
+        <v>42</v>
+      </c>
+      <c r="C68">
+        <v>320</v>
+      </c>
+      <c r="D68">
+        <v>28</v>
+      </c>
+      <c r="E68">
+        <v>28</v>
+      </c>
+      <c r="F68">
+        <v>10</v>
+      </c>
+      <c r="G68">
+        <v>40</v>
+      </c>
+      <c r="H68" t="s">
+        <v>14</v>
+      </c>
+      <c r="I68">
+        <v>4</v>
+      </c>
+      <c r="J68" t="s">
+        <v>340</v>
+      </c>
+      <c r="K68" t="s">
+        <v>243</v>
+      </c>
+      <c r="L68" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>245</v>
+      </c>
+      <c r="B69" t="s">
+        <v>42</v>
+      </c>
+      <c r="C69">
+        <v>480</v>
+      </c>
+      <c r="D69">
+        <v>28</v>
+      </c>
+      <c r="E69">
+        <v>64</v>
+      </c>
+      <c r="F69">
+        <v>12</v>
+      </c>
+      <c r="G69">
+        <v>35</v>
+      </c>
+      <c r="H69" t="s">
+        <v>14</v>
+      </c>
+      <c r="I69">
+        <v>4</v>
+      </c>
+      <c r="J69" t="s">
+        <v>341</v>
+      </c>
+      <c r="K69" t="s">
+        <v>246</v>
+      </c>
+      <c r="L69" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>248</v>
+      </c>
+      <c r="B70" t="s">
+        <v>42</v>
+      </c>
+      <c r="C70">
+        <v>380</v>
+      </c>
+      <c r="D70">
+        <v>42</v>
+      </c>
+      <c r="E70">
+        <v>12</v>
+      </c>
+      <c r="F70">
+        <v>14</v>
+      </c>
+      <c r="G70">
+        <v>75</v>
+      </c>
+      <c r="H70" t="s">
+        <v>33</v>
+      </c>
+      <c r="I70">
+        <v>4</v>
+      </c>
+      <c r="J70" t="s">
+        <v>342</v>
+      </c>
+      <c r="K70" t="s">
+        <v>249</v>
+      </c>
+      <c r="L70" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>251</v>
+      </c>
+      <c r="B71" t="s">
+        <v>42</v>
+      </c>
+      <c r="C71">
+        <v>340</v>
+      </c>
+      <c r="D71">
+        <v>10</v>
+      </c>
+      <c r="E71">
+        <v>52</v>
+      </c>
+      <c r="F71">
+        <v>10</v>
+      </c>
+      <c r="G71">
+        <v>40</v>
+      </c>
+      <c r="H71" t="s">
+        <v>14</v>
+      </c>
+      <c r="I71">
+        <v>4</v>
+      </c>
+      <c r="J71" t="s">
+        <v>343</v>
+      </c>
+      <c r="K71" t="s">
+        <v>252</v>
+      </c>
+      <c r="L71" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>254</v>
+      </c>
+      <c r="B72" t="s">
+        <v>51</v>
+      </c>
+      <c r="C72">
+        <v>280</v>
+      </c>
+      <c r="D72">
+        <v>8</v>
+      </c>
+      <c r="E72">
+        <v>36</v>
+      </c>
+      <c r="F72">
+        <v>12</v>
+      </c>
+      <c r="G72">
+        <v>25</v>
+      </c>
+      <c r="H72" t="s">
+        <v>33</v>
+      </c>
+      <c r="I72">
+        <v>6</v>
+      </c>
+      <c r="J72" t="s">
+        <v>344</v>
+      </c>
+      <c r="K72" t="s">
+        <v>255</v>
+      </c>
+      <c r="L72" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>257</v>
+      </c>
+      <c r="B73" t="s">
+        <v>51</v>
+      </c>
+      <c r="C73">
+        <v>240</v>
+      </c>
+      <c r="D73">
+        <v>4</v>
+      </c>
+      <c r="E73">
+        <v>38</v>
+      </c>
+      <c r="F73">
+        <v>9</v>
+      </c>
+      <c r="G73">
+        <v>20</v>
+      </c>
+      <c r="H73" t="s">
+        <v>14</v>
+      </c>
+      <c r="I73">
+        <v>4</v>
+      </c>
+      <c r="J73" t="s">
+        <v>345</v>
+      </c>
+      <c r="K73" t="s">
+        <v>258</v>
+      </c>
+      <c r="L73" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>260</v>
+      </c>
+      <c r="B74" t="s">
+        <v>51</v>
+      </c>
+      <c r="C74">
+        <v>160</v>
+      </c>
+      <c r="D74">
+        <v>3</v>
+      </c>
+      <c r="E74">
+        <v>28</v>
+      </c>
+      <c r="F74">
+        <v>4</v>
+      </c>
+      <c r="G74">
+        <v>20</v>
+      </c>
+      <c r="H74" t="s">
+        <v>14</v>
+      </c>
+      <c r="I74">
+        <v>4</v>
+      </c>
+      <c r="J74" t="s">
+        <v>346</v>
+      </c>
+      <c r="K74" t="s">
+        <v>261</v>
+      </c>
+      <c r="L74" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>263</v>
+      </c>
+      <c r="B75" t="s">
+        <v>51</v>
+      </c>
+      <c r="C75">
+        <v>220</v>
+      </c>
+      <c r="D75">
+        <v>2</v>
+      </c>
+      <c r="E75">
+        <v>36</v>
+      </c>
+      <c r="F75">
+        <v>8</v>
+      </c>
+      <c r="G75">
+        <v>30</v>
+      </c>
+      <c r="H75" t="s">
+        <v>14</v>
+      </c>
+      <c r="I75">
+        <v>12</v>
+      </c>
+      <c r="J75" t="s">
+        <v>347</v>
+      </c>
+      <c r="K75" t="s">
+        <v>264</v>
+      </c>
+      <c r="L75" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>266</v>
+      </c>
+      <c r="B76" t="s">
+        <v>51</v>
+      </c>
+      <c r="C76">
+        <v>190</v>
+      </c>
+      <c r="D76">
+        <v>4</v>
+      </c>
+      <c r="E76">
+        <v>34</v>
+      </c>
+      <c r="F76">
+        <v>5</v>
+      </c>
+      <c r="G76">
+        <v>20</v>
+      </c>
+      <c r="H76" t="s">
+        <v>14</v>
+      </c>
+      <c r="I76">
+        <v>10</v>
+      </c>
+      <c r="J76" t="s">
+        <v>348</v>
+      </c>
+      <c r="K76" t="s">
+        <v>267</v>
+      </c>
+      <c r="L76" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>269</v>
+      </c>
+      <c r="B77" t="s">
+        <v>51</v>
+      </c>
+      <c r="C77">
+        <v>280</v>
+      </c>
+      <c r="D77">
+        <v>6</v>
+      </c>
+      <c r="E77">
+        <v>52</v>
+      </c>
+      <c r="F77">
+        <v>6</v>
+      </c>
+      <c r="G77">
+        <v>45</v>
+      </c>
+      <c r="H77" t="s">
+        <v>33</v>
+      </c>
+      <c r="I77">
+        <v>8</v>
+      </c>
+      <c r="J77" t="s">
+        <v>349</v>
+      </c>
+      <c r="K77" t="s">
+        <v>270</v>
+      </c>
+      <c r="L77" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>272</v>
+      </c>
+      <c r="B78" t="s">
+        <v>51</v>
+      </c>
+      <c r="C78">
+        <v>200</v>
+      </c>
+      <c r="D78">
+        <v>7</v>
+      </c>
+      <c r="E78">
+        <v>26</v>
+      </c>
+      <c r="F78">
+        <v>8</v>
+      </c>
+      <c r="G78">
+        <v>25</v>
+      </c>
+      <c r="H78" t="s">
+        <v>14</v>
+      </c>
+      <c r="I78">
+        <v>8</v>
+      </c>
+      <c r="J78" t="s">
+        <v>350</v>
+      </c>
+      <c r="K78" t="s">
+        <v>273</v>
+      </c>
+      <c r="L78" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>275</v>
+      </c>
+      <c r="B79" t="s">
+        <v>51</v>
+      </c>
+      <c r="C79">
+        <v>170</v>
+      </c>
+      <c r="D79">
+        <v>3</v>
+      </c>
+      <c r="E79">
+        <v>32</v>
+      </c>
+      <c r="F79">
+        <v>4</v>
+      </c>
+      <c r="G79">
+        <v>30</v>
+      </c>
+      <c r="H79" t="s">
+        <v>14</v>
+      </c>
+      <c r="I79">
+        <v>10</v>
+      </c>
+      <c r="J79" t="s">
+        <v>351</v>
+      </c>
+      <c r="K79" t="s">
+        <v>276</v>
+      </c>
+      <c r="L79" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>278</v>
+      </c>
+      <c r="B80" t="s">
+        <v>51</v>
+      </c>
+      <c r="C80">
+        <v>310</v>
+      </c>
+      <c r="D80">
+        <v>8</v>
+      </c>
+      <c r="E80">
+        <v>42</v>
+      </c>
+      <c r="F80">
+        <v>12</v>
+      </c>
+      <c r="G80">
+        <v>20</v>
+      </c>
+      <c r="H80" t="s">
+        <v>14</v>
+      </c>
+      <c r="I80">
+        <v>4</v>
+      </c>
+      <c r="J80" t="s">
+        <v>352</v>
+      </c>
+      <c r="K80" t="s">
+        <v>279</v>
+      </c>
+      <c r="L80" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>281</v>
+      </c>
+      <c r="B81" t="s">
+        <v>51</v>
+      </c>
+      <c r="C81">
+        <v>240</v>
+      </c>
+      <c r="D81">
+        <v>6</v>
+      </c>
+      <c r="E81">
+        <v>46</v>
+      </c>
+      <c r="F81">
+        <v>4</v>
+      </c>
+      <c r="G81">
+        <v>30</v>
+      </c>
+      <c r="H81" t="s">
+        <v>14</v>
+      </c>
+      <c r="I81">
+        <v>6</v>
+      </c>
+      <c r="J81" t="s">
+        <v>353</v>
+      </c>
+      <c r="K81" t="s">
+        <v>282</v>
+      </c>
+      <c r="L81" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>284</v>
+      </c>
+      <c r="B82" t="s">
+        <v>51</v>
+      </c>
+      <c r="C82">
+        <v>180</v>
+      </c>
+      <c r="D82">
+        <v>12</v>
+      </c>
+      <c r="E82">
+        <v>24</v>
+      </c>
+      <c r="F82">
+        <v>4</v>
+      </c>
+      <c r="G82">
+        <v>120</v>
+      </c>
+      <c r="H82" t="s">
+        <v>28</v>
+      </c>
+      <c r="I82">
+        <v>8</v>
+      </c>
+      <c r="J82" t="s">
+        <v>354</v>
+      </c>
+      <c r="K82" t="s">
+        <v>285</v>
+      </c>
+      <c r="L82" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>287</v>
+      </c>
+      <c r="B83" t="s">
+        <v>51</v>
+      </c>
+      <c r="C83">
+        <v>340</v>
+      </c>
+      <c r="D83">
+        <v>6</v>
+      </c>
+      <c r="E83">
+        <v>58</v>
+      </c>
+      <c r="F83">
+        <v>10</v>
+      </c>
+      <c r="G83">
+        <v>45</v>
+      </c>
+      <c r="H83" t="s">
+        <v>33</v>
+      </c>
+      <c r="I83">
+        <v>8</v>
+      </c>
+      <c r="J83" t="s">
+        <v>355</v>
+      </c>
+      <c r="K83" t="s">
+        <v>288</v>
+      </c>
+      <c r="L83" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>290</v>
+      </c>
+      <c r="B84" t="s">
+        <v>51</v>
+      </c>
+      <c r="C84">
+        <v>380</v>
+      </c>
+      <c r="D84">
+        <v>7</v>
+      </c>
+      <c r="E84">
+        <v>62</v>
+      </c>
+      <c r="F84">
+        <v>12</v>
+      </c>
+      <c r="G84">
+        <v>40</v>
+      </c>
+      <c r="H84" t="s">
+        <v>33</v>
+      </c>
+      <c r="I84">
+        <v>8</v>
+      </c>
+      <c r="J84" t="s">
+        <v>356</v>
+      </c>
+      <c r="K84" t="s">
+        <v>291</v>
+      </c>
+      <c r="L84" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>293</v>
+      </c>
+      <c r="B85" t="s">
+        <v>51</v>
+      </c>
+      <c r="C85">
+        <v>120</v>
+      </c>
+      <c r="D85">
+        <v>2</v>
+      </c>
+      <c r="E85">
+        <v>28</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>60</v>
+      </c>
+      <c r="H85" t="s">
+        <v>33</v>
+      </c>
+      <c r="I85">
+        <v>20</v>
+      </c>
+      <c r="J85" t="s">
+        <v>357</v>
+      </c>
+      <c r="K85" t="s">
+        <v>294</v>
+      </c>
+      <c r="L85" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>296</v>
+      </c>
+      <c r="B86" t="s">
+        <v>51</v>
+      </c>
+      <c r="C86">
+        <v>360</v>
+      </c>
+      <c r="D86">
+        <v>8</v>
+      </c>
+      <c r="E86">
+        <v>54</v>
+      </c>
+      <c r="F86">
+        <v>14</v>
+      </c>
+      <c r="G86">
+        <v>50</v>
+      </c>
+      <c r="H86" t="s">
+        <v>33</v>
+      </c>
+      <c r="I86">
+        <v>8</v>
+      </c>
+      <c r="J86" t="s">
+        <v>358</v>
+      </c>
+      <c r="K86" t="s">
+        <v>297</v>
+      </c>
+      <c r="L86" t="s">
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -1745,6 +4745,8 @@
     <hyperlink ref="J3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="J7" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="J11" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="J42" r:id="rId4" xr:uid="{FBA11BA3-1CBB-4433-ADDD-B99F518C7497}"/>
+    <hyperlink ref="J44" r:id="rId5" xr:uid="{435BE196-7B32-4E92-880F-17CE2C30B177}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
